--- a/исходные_данные/Данные_019.xlsx
+++ b/исходные_данные/Данные_019.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="травостой" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="вода" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="молоко" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="микробиота" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="металлы" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="микробиота" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'выезды'!$A$1:$D$3</definedName>
@@ -23,7 +24,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'травостой'!$A$1:$R$89</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'вода'!$A$1:$M$89</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'молоко'!$A$1:$R$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'микробиота'!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'микробиота'!$A$1:$E$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -69,9 +70,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -439,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -512,6 +516,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>После правок сохраните файл и пересоберите сайт: python3 скрипты/run_all.py (или попросите Claude).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Лист «металлы» – тяжёлые металлы и микроэлементы в воде (лаборатория, проба = точка воды в выезде). «&lt;0,0001» – ниже предела обнаружения, «&gt;5» – выше диапазона прибора, «нет» – нет данных.</t>
         </is>
       </c>
     </row>
@@ -15106,6 +15117,4296 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:AL25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="11" customWidth="1" min="23" max="23"/>
+    <col width="11" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="11" customWidth="1" min="26" max="26"/>
+    <col width="11" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="11" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
+    <col width="11" customWidth="1" min="31" max="31"/>
+    <col width="11" customWidth="1" min="32" max="32"/>
+    <col width="11" customWidth="1" min="33" max="33"/>
+    <col width="11" customWidth="1" min="34" max="34"/>
+    <col width="11" customWidth="1" min="35" max="35"/>
+    <col width="11" customWidth="1" min="36" max="36"/>
+    <col width="11" customWidth="1" min="37" max="37"/>
+    <col width="11" customWidth="1" min="38" max="38"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Сельский округ</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>ТС</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Выезд</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Дата отбора</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Рег. № лаборатории</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Дата анализа</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>pH (лаб.)</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Электропроводность COND, mS</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>TDS (лаб.), г/л</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Солёность SALT, ppt</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>ОВП (ORP), mV</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Ag, мг/л</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Al, мг/л</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>As, мг/л</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>B, мг/л</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>Ba, мг/л</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Be, мг/л</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>Ca, мг/л</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>Cd, мг/л</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>Co, мг/л</t>
+        </is>
+      </c>
+      <c r="U1" s="2" t="inlineStr">
+        <is>
+          <t>Cr, мг/л</t>
+        </is>
+      </c>
+      <c r="V1" s="2" t="inlineStr">
+        <is>
+          <t>Cu, мг/л</t>
+        </is>
+      </c>
+      <c r="W1" s="2" t="inlineStr">
+        <is>
+          <t>Fe, мг/л</t>
+        </is>
+      </c>
+      <c r="X1" s="2" t="inlineStr">
+        <is>
+          <t>K, мг/л</t>
+        </is>
+      </c>
+      <c r="Y1" s="2" t="inlineStr">
+        <is>
+          <t>Mg, мг/л</t>
+        </is>
+      </c>
+      <c r="Z1" s="2" t="inlineStr">
+        <is>
+          <t>Mn, мг/л</t>
+        </is>
+      </c>
+      <c r="AA1" s="2" t="inlineStr">
+        <is>
+          <t>Mo, мг/л</t>
+        </is>
+      </c>
+      <c r="AB1" s="2" t="inlineStr">
+        <is>
+          <t>Na, мг/л</t>
+        </is>
+      </c>
+      <c r="AC1" s="2" t="inlineStr">
+        <is>
+          <t>Ni, мг/л</t>
+        </is>
+      </c>
+      <c r="AD1" s="2" t="inlineStr">
+        <is>
+          <t>Pb, мг/л</t>
+        </is>
+      </c>
+      <c r="AE1" s="2" t="inlineStr">
+        <is>
+          <t>Sb, мг/л</t>
+        </is>
+      </c>
+      <c r="AF1" s="2" t="inlineStr">
+        <is>
+          <t>Se, мг/л</t>
+        </is>
+      </c>
+      <c r="AG1" s="2" t="inlineStr">
+        <is>
+          <t>Si, мг/л</t>
+        </is>
+      </c>
+      <c r="AH1" s="2" t="inlineStr">
+        <is>
+          <t>Sr, мг/л</t>
+        </is>
+      </c>
+      <c r="AI1" s="2" t="inlineStr">
+        <is>
+          <t>Ti, мг/л</t>
+        </is>
+      </c>
+      <c r="AJ1" s="2" t="inlineStr">
+        <is>
+          <t>Tl, мг/л</t>
+        </is>
+      </c>
+      <c r="AK1" s="2" t="inlineStr">
+        <is>
+          <t>V, мг/л</t>
+        </is>
+      </c>
+      <c r="AL1" s="2" t="inlineStr">
+        <is>
+          <t>Zn, мг/л</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Каратерекский</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Сентябрь 2026</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>18.09.2026</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>331</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>08–09.10.2026</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K2" t="n">
+        <v>142.2</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0101</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>0.237</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.246</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Каратерекский</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Сентябрь 2026</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>18.09.2026</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>332</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>08–09.10.2026</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="K3" t="n">
+        <v>154</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.0492</v>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Каратерекский</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Сентябрь 2026</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>18.09.2026</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>333</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>08–09.10.2026</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K4" t="n">
+        <v>140</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0123</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.008200000000000001</v>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Каратерекский</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Сентябрь 2026</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>18.09.2026</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>334</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>08–09.10.2026</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>8.48</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K5" t="n">
+        <v>133.2</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.422</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Коктерекский</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Сентябрь 2026</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>18.09.2026</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>335</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>08–09.10.2026</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.552</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="K6" t="n">
+        <v>135</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Коктерекский</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Сентябрь 2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>18.09.2026</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>336</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>08–09.10.2026</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.196</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="K7" t="n">
+        <v>129</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0496</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>0.0243</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Коктерекский</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Сентябрь 2026</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>18.09.2026</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>337</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>08–09.10.2026</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K8" t="n">
+        <v>133</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0561</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>0.0781</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Коктерекский</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Сентябрь 2026</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>18.09.2026</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>338</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>08–09.10.2026</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="K9" t="n">
+        <v>107</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0636</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Кайратский</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Сентябрь 2026</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>18.09.2026</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>339</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>08–09.10.2026</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K10" t="n">
+        <v>121</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.0242</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Кайратский</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Сентябрь 2026</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>18.09.2026</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>340</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>08–09.10.2026</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="K11" t="n">
+        <v>136</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>0.178</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Кайратский</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Сентябрь 2026</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>18.09.2026</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>341</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>08–09.10.2026</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="H12" t="n">
+        <v>9.92</v>
+      </c>
+      <c r="I12" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="J12" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="K12" t="n">
+        <v>144</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>0.5580000000000001</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.0562</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Кайратский</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Сентябрь 2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>18.09.2026</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>342</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>08–09.10.2026</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K13" t="n">
+        <v>94</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.0566</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Кулыкольский</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Сентябрь 2026</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>18.09.2026</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>343</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>08–09.10.2026</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.045</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.728</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="K14" t="n">
+        <v>113</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>0.0827</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="W14" t="n">
+        <v>0.0771</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.578</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Кулыкольский</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Сентябрь 2026</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>18.09.2026</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>344</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>08–09.10.2026</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K15" t="n">
+        <v>129</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>0.483</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.0712</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="W15" t="n">
+        <v>0.0929</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Кулыкольский</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Сентябрь 2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>18.09.2026</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>345</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>08–09.10.2026</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="H16" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="I16" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="K16" t="n">
+        <v>140</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.06759999999999999</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="W16" t="n">
+        <v>0.0919</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.478</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Кулыкольский</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Сентябрь 2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>18.09.2026</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>346</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>08–09.10.2026</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="K17" t="n">
+        <v>122</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.0699</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Кишкенекольский</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Сентябрь 2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>17.09.2026</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>347</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>08–09.10.2026</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.198</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K18" t="n">
+        <v>129</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.0502</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Кишкенекольский</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Сентябрь 2026</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>17.09.2026</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>348</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>08–09.10.2026</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.5580000000000001</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="K19" t="n">
+        <v>107</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.06419999999999999</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Кишкенекольский</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Сентябрь 2026</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>17.09.2026</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>349</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>08–09.10.2026</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="H20" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="I20" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="K20" t="n">
+        <v>130</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="W20" t="n">
+        <v>0.0804</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.0249</v>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>0.823</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Кишкенекольский</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Сентябрь 2026</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>17.09.2026</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>350</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>08–09.10.2026</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.245</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="K21" t="n">
+        <v>127</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0.06619999999999999</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="W21" t="n">
+        <v>0.0537</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Z21" t="n">
+        <v>0.0167</v>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0.8090000000000001</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Карасуский</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Сентябрь 2026</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>18.09.2026</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>351</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>08–09.10.2026</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="K22" t="n">
+        <v>131</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>0.253</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="W22" t="n">
+        <v>0.0655</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Z22" t="n">
+        <v>0.0249</v>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Карасуский</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Сентябрь 2026</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>18.09.2026</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>352</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>08–09.10.2026</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="K23" t="n">
+        <v>139</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Карасуский</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Сентябрь 2026</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>18.09.2026</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>353</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>08–09.10.2026</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.314</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="K24" t="n">
+        <v>130</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>0.249</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Карасуский</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Сентябрь 2026</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>18.09.2026</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>354</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>08–09.10.2026</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.0774</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K25" t="n">
+        <v>128</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>&gt;5</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>&lt;0,0001</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
